--- a/reports/agent-report.xlsx
+++ b/reports/agent-report.xlsx
@@ -447,7 +447,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>64143</t>
+          <t>64147</t>
         </is>
       </c>
     </row>
@@ -459,7 +459,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>11f53f99-df03-4073-8c00-d72e6554ece1</t>
+          <t>8cb0291a-8746-443e-a911-02123d8d69f7</t>
         </is>
       </c>
     </row>

--- a/reports/agent-report.xlsx
+++ b/reports/agent-report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -442,60 +442,73 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>jobId</t>
+          <t>content</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>64147</t>
+          <t>{
+  "name": "Experience wireframing Agent_2026-10-01_17-29-31.html",
+  "path": "reports/Experience wireframing Agent_2026-10-01_17-29-31.html",
+  "sha": "0c44115fadeb77e2806ad2fa70f1f8288c0b2206",
+  "size": 13546,
+  "url": "https://api.github.com/repos/Vishalgaurav0610/AgenticUX/contents/reports/Experience%20wireframing%20Agent_2026-10-01_17-29-31.html?ref=main",
+  "html_url": "https://github.com/Vishalgaurav0610/AgenticUX/blob/main/reports/Experience%20wireframing%20Agent_2026-10-01_17-29-31.html",
+  "git_url": "https://api.github.com/repos/Vishalgaurav0610/AgenticUX/git/blobs/0c44115fadeb77e2806ad2fa70f1f8288c0b2206",
+  "download_url": "https://raw.githubusercontent.com/Vishalgaurav0610/AgenticUX/main/reports/Experience%20wireframing%20Agent_2026-10-01_17-29-31.html",
+  "type": "file",
+  "_links": {
+    "self": "https://api.github.com/repos/Vishalgaurav0610/AgenticUX/contents/reports/Experience%20wireframing%20Agent_2026-10-01_17-29-31.html?ref=main",
+    "git": "https://api.github.com/repos/Vishalgaurav0610/AgenticUX/git/blobs/0c44115fadeb77e2806ad2fa70f1f8288c0b2206",
+    "html": "https://github.com/Vishalgaurav0610/AgenticUX/blob/main/reports/Experience%20wireframing%20Agent_2026-10-01_17-29-31.html"
+  }
+}</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>agentExecutionId</t>
+          <t>commit</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>8cb0291a-8746-443e-a911-02123d8d69f7</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>message</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Agent job submitted successfully</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>httpStatus</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>200 OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
+          <t>{
+  "sha": "20168672d45f98279744a0db8bf2b1db4c77e21e",
+  "node_id": "C_kwDOSabqSNoAKDIwMTY4NjcyZDQ1Zjk4Mjc5NzQ0YTBkYjhiZjJiMWRiNGM3N2UyMWU",
+  "url": "https://api.github.com/repos/Vishalgaurav0610/AgenticUX/git/commits/20168672d45f98279744a0db8bf2b1db4c77e21e",
+  "html_url": "https://github.com/Vishalgaurav0610/AgenticUX/commit/20168672d45f98279744a0db8bf2b1db4c77e21e",
+  "author": {
+    "name": "Vishalgaurav0610",
+    "email": "vishal.gaurav@ascendion.com",
+    "date": "2026-10-01T11:59:27Z"
+  },
+  "committer": {
+    "name": "Vishalgaurav0610",
+    "email": "vishal.gaurav@ascendion.com",
+    "date": "2026-10-01T11:59:27Z"
+  },
+  "tree": {
+    "sha": "09efcba1e36ed41562f57a457403199b6765d049",
+    "url": "https://api.github.com/repos/Vishalgaurav0610/AgenticUX/git/trees/09efcba1e36ed41562f57a457403199b6765d049"
+  },
+  "message": "Add AAVA agent HTML report - 2026-10-01_17-29-31",
+  "parents": [
+    {
+      "sha": "1a56923aeadcdf97bb7677b914f97399d89adefb",
+      "url": "https://api.github.com/repos/Vishalgaurav0610/AgenticUX/git/commits/1a56923aeadcdf97bb7677b914f97399d89adefb",
+      "html_url": "https://github.com/Vishalgaurav0610/AgenticUX/commit/1a56923aeadcdf97bb7677b914f97399d89adefb"
+    }
+  ],
+  "verification": {
+    "verified": false,
+    "reason": "unsigned",
+    "signature": null,
+    "payload": null,
+    "verified_at": null
+  }
+}</t>
         </is>
       </c>
     </row>
